--- a/datos/valido_sin_unidades.xlsx
+++ b/datos/valido_sin_unidades.xlsx
@@ -433,7 +433,7 @@
         <v>-1</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.758028020390451e-06</v>
+        <v>-1.712292419091742e-06</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +441,7 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.69319586464304e-06</v>
+        <v>-1.432044576163101e-06</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +449,7 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.536293429255772e-06</v>
+        <v>-1.377884739220399e-06</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +457,7 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.636555115259505e-06</v>
+        <v>-1.500715898617365e-06</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +465,7 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.347188373749221e-06</v>
+        <v>-1.361806349386038e-06</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +473,7 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.59947385837889e-06</v>
+        <v>-1.289950205646787e-06</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +481,7 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.224598038247485e-06</v>
+        <v>-1.166191477986032e-06</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.50984858718875e-06</v>
+        <v>-1.579370926770147e-06</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +497,7 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.59424173012948e-06</v>
+        <v>-1.247285710329999e-06</v>
       </c>
     </row>
     <row r="11">
@@ -505,7 +505,7 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.473950477934273e-06</v>
+        <v>-1.470177043224249e-06</v>
       </c>
     </row>
     <row r="12">
@@ -513,7 +513,7 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.540694889638359e-06</v>
+        <v>-1.7071969171789e-06</v>
       </c>
     </row>
     <row r="13">
@@ -521,7 +521,7 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.372690663453701e-06</v>
+        <v>-1.606460540609302e-06</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +529,7 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.42076223960272e-06</v>
+        <v>-1.644994761933046e-06</v>
       </c>
     </row>
     <row r="15">
@@ -537,7 +537,7 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.715189792788375e-06</v>
+        <v>-1.423807992829951e-06</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +545,7 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.67396391705667e-06</v>
+        <v>-1.341080448987492e-06</v>
       </c>
     </row>
     <row r="17">
@@ -553,7 +553,7 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.506420962646995e-06</v>
+        <v>-1.335821647126643e-06</v>
       </c>
     </row>
     <row r="18">
@@ -561,7 +561,7 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.489556254031707e-06</v>
+        <v>-1.792307380399477e-06</v>
       </c>
     </row>
     <row r="19">
@@ -569,7 +569,7 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.597205919796447e-06</v>
+        <v>-1.687973981013294e-06</v>
       </c>
     </row>
     <row r="20">
@@ -577,7 +577,7 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.743035193000048e-06</v>
+        <v>-1.402253887070225e-06</v>
       </c>
     </row>
     <row r="21">
@@ -585,7 +585,7 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.227951089477827e-06</v>
+        <v>-1.545035618424038e-06</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +593,7 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.748062739281002e-06</v>
+        <v>-1.595189180517406e-06</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +601,7 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.410555700609019e-06</v>
+        <v>-1.404103677861395e-06</v>
       </c>
     </row>
     <row r="24">
@@ -609,7 +609,7 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.523238293758567e-06</v>
+        <v>-1.379555320766155e-06</v>
       </c>
     </row>
     <row r="25">
@@ -617,7 +617,7 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.4258849140297e-06</v>
+        <v>-1.561496980330766e-06</v>
       </c>
     </row>
     <row r="26">
@@ -625,7 +625,7 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.631085953584385e-06</v>
+        <v>-1.595594233852267e-06</v>
       </c>
     </row>
     <row r="27">
@@ -633,7 +633,7 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.498456757652397e-06</v>
+        <v>-1.344848967919252e-06</v>
       </c>
     </row>
     <row r="28">
@@ -641,7 +641,7 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.563337165646793e-06</v>
+        <v>-1.492634851343576e-06</v>
       </c>
     </row>
     <row r="29">
@@ -649,7 +649,7 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.615728122346375e-06</v>
+        <v>-1.770302965058753e-06</v>
       </c>
     </row>
     <row r="30">
@@ -657,7 +657,7 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="B30" t="n">
-        <v>-1.44807354421619e-06</v>
+        <v>-1.798078043864689e-06</v>
       </c>
     </row>
     <row r="31">
@@ -665,7 +665,7 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.545232267986923e-06</v>
+        <v>-1.189344722529858e-06</v>
       </c>
     </row>
     <row r="32">
@@ -673,7 +673,7 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.427718171348877e-06</v>
+        <v>-1.237633393044948e-06</v>
       </c>
     </row>
     <row r="33">
@@ -681,7 +681,7 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.003846912330523e-06</v>
+        <v>-1.519177808205207e-06</v>
       </c>
     </row>
     <row r="34">
@@ -689,7 +689,7 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.40568431938054e-06</v>
+        <v>-1.489620836467144e-06</v>
       </c>
     </row>
     <row r="35">
@@ -697,7 +697,7 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.187756971756703e-06</v>
+        <v>-1.564312425479831e-06</v>
       </c>
     </row>
     <row r="36">
@@ -705,7 +705,7 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.619193400934133e-06</v>
+        <v>-1.258210538889084e-06</v>
       </c>
     </row>
     <row r="37">
@@ -713,7 +713,7 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.669087906729658e-06</v>
+        <v>-1.464612220023091e-06</v>
       </c>
     </row>
     <row r="38">
@@ -721,7 +721,7 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.459699367977664e-06</v>
+        <v>-1.30350183625987e-06</v>
       </c>
     </row>
     <row r="39">
@@ -729,7 +729,7 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.210034990432649e-06</v>
+        <v>-1.241974733543254e-06</v>
       </c>
     </row>
     <row r="40">
@@ -737,7 +737,7 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.058786209729831e-06</v>
+        <v>-1.400010880071123e-06</v>
       </c>
     </row>
     <row r="41">
@@ -745,7 +745,7 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.339407105199022e-06</v>
+        <v>-1.3608409261866e-06</v>
       </c>
     </row>
     <row r="42">
@@ -753,7 +753,7 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="B42" t="n">
-        <v>-9.737971330681434e-07</v>
+        <v>-1.406141371982233e-06</v>
       </c>
     </row>
     <row r="43">
@@ -761,7 +761,7 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.124049076096352e-06</v>
+        <v>-1.402223994822067e-06</v>
       </c>
     </row>
     <row r="44">
@@ -769,7 +769,7 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.276319616204668e-06</v>
+        <v>-1.269555099076554e-06</v>
       </c>
     </row>
     <row r="45">
@@ -777,7 +777,7 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.206025271916542e-06</v>
+        <v>-1.013983653026599e-06</v>
       </c>
     </row>
     <row r="46">
@@ -785,7 +785,7 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="B46" t="n">
-        <v>-1.045186243448915e-06</v>
+        <v>-8.002623733075869e-07</v>
       </c>
     </row>
     <row r="47">
@@ -793,7 +793,7 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="B47" t="n">
-        <v>-9.881165241816256e-07</v>
+        <v>-7.760843254628716e-07</v>
       </c>
     </row>
     <row r="48">
@@ -801,7 +801,7 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="B48" t="n">
-        <v>-7.026145825316699e-07</v>
+        <v>-8.128197707422473e-07</v>
       </c>
     </row>
     <row r="49">
@@ -809,7 +809,7 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="B49" t="n">
-        <v>-5.18236716584794e-07</v>
+        <v>-5.878008319186361e-07</v>
       </c>
     </row>
     <row r="50">
@@ -817,7 +817,7 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="B50" t="n">
-        <v>-2.913676558537179e-07</v>
+        <v>-5.750891986302694e-07</v>
       </c>
     </row>
     <row r="51">
@@ -825,7 +825,7 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="B51" t="n">
-        <v>-9.951961678596721e-08</v>
+        <v>-2.415316715833149e-07</v>
       </c>
     </row>
     <row r="52">
@@ -833,7 +833,7 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="B52" t="n">
-        <v>1.694781135567585e-07</v>
+        <v>-9.140891699249136e-08</v>
       </c>
     </row>
     <row r="53">
@@ -841,7 +841,7 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="B53" t="n">
-        <v>5.812313121125108e-07</v>
+        <v>5.740500834657922e-07</v>
       </c>
     </row>
     <row r="54">
@@ -849,7 +849,7 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="B54" t="n">
-        <v>9.369175200896264e-07</v>
+        <v>9.525237548330164e-07</v>
       </c>
     </row>
     <row r="55">
@@ -857,7 +857,7 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="B55" t="n">
-        <v>1.503437202477505e-06</v>
+        <v>1.462042022067014e-06</v>
       </c>
     </row>
     <row r="56">
@@ -865,7 +865,7 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="B56" t="n">
-        <v>2.454617903392006e-06</v>
+        <v>2.095813248362621e-06</v>
       </c>
     </row>
     <row r="57">
@@ -873,7 +873,7 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="B57" t="n">
-        <v>3.175844226370455e-06</v>
+        <v>3.077827138493962e-06</v>
       </c>
     </row>
     <row r="58">
@@ -881,7 +881,7 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="B58" t="n">
-        <v>4.168196109225296e-06</v>
+        <v>3.926596639532155e-06</v>
       </c>
     </row>
     <row r="59">
@@ -889,7 +889,7 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="B59" t="n">
-        <v>5.407259431974136e-06</v>
+        <v>5.298084522531493e-06</v>
       </c>
     </row>
     <row r="60">
@@ -897,7 +897,7 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="B60" t="n">
-        <v>6.954325615011145e-06</v>
+        <v>6.776907368249621e-06</v>
       </c>
     </row>
     <row r="61">
@@ -905,7 +905,7 @@
         <v>0.191919191919192</v>
       </c>
       <c r="B61" t="n">
-        <v>8.568229862153347e-06</v>
+        <v>8.868037048532388e-06</v>
       </c>
     </row>
     <row r="62">
@@ -913,7 +913,7 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="B62" t="n">
-        <v>1.093322081573866e-05</v>
+        <v>1.108289941839332e-05</v>
       </c>
     </row>
     <row r="63">
@@ -921,7 +921,7 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="B63" t="n">
-        <v>1.37111615848339e-05</v>
+        <v>1.382390786867322e-05</v>
       </c>
     </row>
     <row r="64">
@@ -929,7 +929,7 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="B64" t="n">
-        <v>1.713660789748331e-05</v>
+        <v>1.741548806674379e-05</v>
       </c>
     </row>
     <row r="65">
@@ -937,7 +937,7 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="B65" t="n">
-        <v>2.140717727437383e-05</v>
+        <v>2.15155860653159e-05</v>
       </c>
     </row>
     <row r="66">
@@ -945,7 +945,7 @@
         <v>0.292929292929293</v>
       </c>
       <c r="B66" t="n">
-        <v>2.658323014056471e-05</v>
+        <v>2.656165466693766e-05</v>
       </c>
     </row>
     <row r="67">
@@ -953,7 +953,7 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="B67" t="n">
-        <v>3.269428794530127e-05</v>
+        <v>3.242801421429797e-05</v>
       </c>
     </row>
     <row r="68">
@@ -961,7 +961,7 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="B68" t="n">
-        <v>4.05299243014097e-05</v>
+        <v>4.048128565545624e-05</v>
       </c>
     </row>
     <row r="69">
@@ -969,7 +969,7 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="B69" t="n">
-        <v>4.979363883266775e-05</v>
+        <v>5.003720706943225e-05</v>
       </c>
     </row>
     <row r="70">
@@ -977,7 +977,7 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="B70" t="n">
-        <v>6.166380216626379e-05</v>
+        <v>6.151555263173121e-05</v>
       </c>
     </row>
     <row r="71">
@@ -985,7 +985,7 @@
         <v>0.393939393939394</v>
       </c>
       <c r="B71" t="n">
-        <v>7.575794951253261e-05</v>
+        <v>7.561214582917243e-05</v>
       </c>
     </row>
     <row r="72">
@@ -993,7 +993,7 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="B72" t="n">
-        <v>9.277540492194595e-05</v>
+        <v>9.280732892941171e-05</v>
       </c>
     </row>
     <row r="73">
@@ -1001,7 +1001,7 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0001138668251510055</v>
+        <v>0.000113865544374301</v>
       </c>
     </row>
     <row r="74">
@@ -1009,7 +1009,7 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0001399458163791131</v>
+        <v>0.0001397478539513639</v>
       </c>
     </row>
     <row r="75">
@@ -1017,7 +1017,7 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0001715483733848637</v>
+        <v>0.0001713323132963051</v>
       </c>
     </row>
     <row r="76">
@@ -1025,7 +1025,7 @@
         <v>0.494949494949495</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0002100800676893033</v>
+        <v>0.0002100130282193019</v>
       </c>
     </row>
     <row r="77">
@@ -1033,7 +1033,7 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0002573637909183635</v>
+        <v>0.0002575387373350303</v>
       </c>
     </row>
     <row r="78">
@@ -1041,7 +1041,7 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0003154088940972302</v>
+        <v>0.0003155100429703204</v>
       </c>
     </row>
     <row r="79">
@@ -1049,7 +1049,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0003864832829793709</v>
+        <v>0.0003868260169819277</v>
       </c>
     </row>
     <row r="80">
@@ -1057,7 +1057,7 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0004731184758242975</v>
+        <v>0.0004733459907301466</v>
       </c>
     </row>
     <row r="81">
@@ -1065,7 +1065,7 @@
         <v>0.595959595959596</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0005797229265168082</v>
+        <v>0.0005798052779649741</v>
       </c>
     </row>
     <row r="82">
@@ -1073,7 +1073,7 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0007097561485397799</v>
+        <v>0.0007095627829878473</v>
       </c>
     </row>
     <row r="83">
@@ -1081,7 +1081,7 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="B83" t="n">
-        <v>0.000868868489573575</v>
+        <v>0.0008688811739596266</v>
       </c>
     </row>
     <row r="84">
@@ -1089,7 +1089,7 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="B84" t="n">
-        <v>0.001064049308397907</v>
+        <v>0.0010642319344498</v>
       </c>
     </row>
     <row r="85">
@@ -1097,7 +1097,7 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="B85" t="n">
-        <v>0.001302337678760222</v>
+        <v>0.001302443751845014</v>
       </c>
     </row>
     <row r="86">
@@ -1105,7 +1105,7 @@
         <v>0.696969696969697</v>
       </c>
       <c r="B86" t="n">
-        <v>0.001594475186196861</v>
+        <v>0.001594062927496364</v>
       </c>
     </row>
     <row r="87">
@@ -1113,7 +1113,7 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="B87" t="n">
-        <v>0.001951650056788976</v>
+        <v>0.001951366262274125</v>
       </c>
     </row>
     <row r="88">
@@ -1121,7 +1121,7 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="B88" t="n">
-        <v>0.002388719507434232</v>
+        <v>0.002388908346430514</v>
       </c>
     </row>
     <row r="89">
@@ -1129,7 +1129,7 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="B89" t="n">
-        <v>0.00292403537495362</v>
+        <v>0.002923668701554566</v>
       </c>
     </row>
     <row r="90">
@@ -1137,7 +1137,7 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="B90" t="n">
-        <v>0.003578980609576918</v>
+        <v>0.00357910666308193</v>
       </c>
     </row>
     <row r="91">
@@ -1145,7 +1145,7 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="B91" t="n">
-        <v>0.004380397331717551</v>
+        <v>0.004380547544919552</v>
       </c>
     </row>
     <row r="92">
@@ -1153,7 +1153,7 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="B92" t="n">
-        <v>0.005361711156854344</v>
+        <v>0.005361693247289966</v>
       </c>
     </row>
     <row r="93">
@@ -1161,7 +1161,7 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="B93" t="n">
-        <v>0.00656247736830347</v>
+        <v>0.006562097899529768</v>
       </c>
     </row>
     <row r="94">
@@ -1169,7 +1169,7 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="B94" t="n">
-        <v>0.008031495411288007</v>
+        <v>0.008031434054084659</v>
       </c>
     </row>
     <row r="95">
@@ -1177,7 +1177,7 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="B95" t="n">
-        <v>0.009830267687205001</v>
+        <v>0.009829831664932634</v>
       </c>
     </row>
     <row r="96">
@@ -1185,7 +1185,7 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="B96" t="n">
-        <v>0.01203122921854918</v>
+        <v>0.01203097232811743</v>
       </c>
     </row>
     <row r="97">
@@ -1193,7 +1193,7 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="B97" t="n">
-        <v>0.01472464210220618</v>
+        <v>0.01472479051928766</v>
       </c>
     </row>
     <row r="98">
@@ -1201,7 +1201,7 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="B98" t="n">
-        <v>0.01802144659965697</v>
+        <v>0.01802134002644562</v>
       </c>
     </row>
     <row r="99">
@@ -1209,7 +1209,7 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="B99" t="n">
-        <v>0.02205610576516964</v>
+        <v>0.02205624653091874</v>
       </c>
     </row>
     <row r="100">
@@ -1217,7 +1217,7 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="B100" t="n">
-        <v>0.0269946565178375</v>
+        <v>0.02699455311882026</v>
       </c>
     </row>
     <row r="101">
@@ -1225,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>0.03303825296252046</v>
+        <v>0.0330381190422584</v>
       </c>
     </row>
   </sheetData>

--- a/datos/valido_sin_unidades.xlsx
+++ b/datos/valido_sin_unidades.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="datos_IV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
         <v>-1</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.712292419091742e-06</v>
+        <v>-1.519227434104136e-06</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +442,7 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.432044576163101e-06</v>
+        <v>-1.561115588306852e-06</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +450,7 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.377884739220399e-06</v>
+        <v>-1.255470996387646e-06</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +458,7 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.500715898617365e-06</v>
+        <v>-1.64785953285502e-06</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +466,7 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.361806349386038e-06</v>
+        <v>-1.344653903722191e-06</v>
       </c>
     </row>
     <row r="7">
@@ -473,7 +474,7 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.289950205646787e-06</v>
+        <v>-1.368896383051833e-06</v>
       </c>
     </row>
     <row r="8">
@@ -481,7 +482,7 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.166191477986032e-06</v>
+        <v>-1.695246821348974e-06</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +490,7 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.579370926770147e-06</v>
+        <v>-1.426964696409526e-06</v>
       </c>
     </row>
     <row r="10">
@@ -497,7 +498,7 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.247285710329999e-06</v>
+        <v>-1.152694880398845e-06</v>
       </c>
     </row>
     <row r="11">
@@ -505,7 +506,7 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.470177043224249e-06</v>
+        <v>-1.464756372196595e-06</v>
       </c>
     </row>
     <row r="12">
@@ -513,7 +514,7 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.7071969171789e-06</v>
+        <v>-1.536315922190911e-06</v>
       </c>
     </row>
     <row r="13">
@@ -521,7 +522,7 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.606460540609302e-06</v>
+        <v>-1.321268585502097e-06</v>
       </c>
     </row>
     <row r="14">
@@ -529,7 +530,7 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.644994761933046e-06</v>
+        <v>-1.496016510136476e-06</v>
       </c>
     </row>
     <row r="15">
@@ -537,7 +538,7 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.423807992829951e-06</v>
+        <v>-1.424734569530483e-06</v>
       </c>
     </row>
     <row r="16">
@@ -545,7 +546,7 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.341080448987492e-06</v>
+        <v>-1.340085431387201e-06</v>
       </c>
     </row>
     <row r="17">
@@ -553,7 +554,7 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.335821647126643e-06</v>
+        <v>-1.471941216230423e-06</v>
       </c>
     </row>
     <row r="18">
@@ -561,7 +562,7 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.792307380399477e-06</v>
+        <v>-1.482173215762295e-06</v>
       </c>
     </row>
     <row r="19">
@@ -569,7 +570,7 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.687973981013294e-06</v>
+        <v>-1.520678171913912e-06</v>
       </c>
     </row>
     <row r="20">
@@ -577,7 +578,7 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.402253887070225e-06</v>
+        <v>-1.529245467951381e-06</v>
       </c>
     </row>
     <row r="21">
@@ -585,7 +586,7 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.545035618424038e-06</v>
+        <v>-1.625952546292414e-06</v>
       </c>
     </row>
     <row r="22">
@@ -593,7 +594,7 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.595189180517406e-06</v>
+        <v>-1.686978380279806e-06</v>
       </c>
     </row>
     <row r="23">
@@ -601,7 +602,7 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.404103677861395e-06</v>
+        <v>-1.295228008084592e-06</v>
       </c>
     </row>
     <row r="24">
@@ -609,7 +610,7 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.379555320766155e-06</v>
+        <v>-1.621985724703675e-06</v>
       </c>
     </row>
     <row r="25">
@@ -617,7 +618,7 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.561496980330766e-06</v>
+        <v>-1.207417273710176e-06</v>
       </c>
     </row>
     <row r="26">
@@ -625,7 +626,7 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.595594233852267e-06</v>
+        <v>-1.43336062366842e-06</v>
       </c>
     </row>
     <row r="27">
@@ -633,7 +634,7 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.344848967919252e-06</v>
+        <v>-1.421830806913712e-06</v>
       </c>
     </row>
     <row r="28">
@@ -641,7 +642,7 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.492634851343576e-06</v>
+        <v>-1.270297195843239e-06</v>
       </c>
     </row>
     <row r="29">
@@ -649,7 +650,7 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="B29" t="n">
-        <v>-1.770302965058753e-06</v>
+        <v>-1.477870331934529e-06</v>
       </c>
     </row>
     <row r="30">
@@ -657,7 +658,7 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="B30" t="n">
-        <v>-1.798078043864689e-06</v>
+        <v>-1.292657144477929e-06</v>
       </c>
     </row>
     <row r="31">
@@ -665,7 +666,7 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.189344722529858e-06</v>
+        <v>-1.546461755706342e-06</v>
       </c>
     </row>
     <row r="32">
@@ -673,7 +674,7 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.237633393044948e-06</v>
+        <v>-1.519505214819601e-06</v>
       </c>
     </row>
     <row r="33">
@@ -681,7 +682,7 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="B33" t="n">
-        <v>-1.519177808205207e-06</v>
+        <v>-1.318038309516224e-06</v>
       </c>
     </row>
     <row r="34">
@@ -689,7 +690,7 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.489620836467144e-06</v>
+        <v>-1.464284213397006e-06</v>
       </c>
     </row>
     <row r="35">
@@ -697,7 +698,7 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.564312425479831e-06</v>
+        <v>-1.656954725621788e-06</v>
       </c>
     </row>
     <row r="36">
@@ -705,7 +706,7 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="B36" t="n">
-        <v>-1.258210538889084e-06</v>
+        <v>-1.390655528254858e-06</v>
       </c>
     </row>
     <row r="37">
@@ -713,7 +714,7 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.464612220023091e-06</v>
+        <v>-1.584650386687599e-06</v>
       </c>
     </row>
     <row r="38">
@@ -721,7 +722,7 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.30350183625987e-06</v>
+        <v>-1.420509316406492e-06</v>
       </c>
     </row>
     <row r="39">
@@ -729,7 +730,7 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.241974733543254e-06</v>
+        <v>-1.542870510465813e-06</v>
       </c>
     </row>
     <row r="40">
@@ -737,7 +738,7 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="B40" t="n">
-        <v>-1.400010880071123e-06</v>
+        <v>-1.378844559083924e-06</v>
       </c>
     </row>
     <row r="41">
@@ -745,7 +746,7 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.3608409261866e-06</v>
+        <v>-1.093686923028429e-06</v>
       </c>
     </row>
     <row r="42">
@@ -753,7 +754,7 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.406141371982233e-06</v>
+        <v>-1.534866130457702e-06</v>
       </c>
     </row>
     <row r="43">
@@ -761,7 +762,7 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.402223994822067e-06</v>
+        <v>-1.198852910644819e-06</v>
       </c>
     </row>
     <row r="44">
@@ -769,7 +770,7 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="B44" t="n">
-        <v>-1.269555099076554e-06</v>
+        <v>-1.226385335098994e-06</v>
       </c>
     </row>
     <row r="45">
@@ -777,7 +778,7 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.013983653026599e-06</v>
+        <v>-9.459591886337722e-07</v>
       </c>
     </row>
     <row r="46">
@@ -785,7 +786,7 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="B46" t="n">
-        <v>-8.002623733075869e-07</v>
+        <v>-8.999899619104323e-07</v>
       </c>
     </row>
     <row r="47">
@@ -793,7 +794,7 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="B47" t="n">
-        <v>-7.760843254628716e-07</v>
+        <v>-1.142106673908157e-06</v>
       </c>
     </row>
     <row r="48">
@@ -801,7 +802,7 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="B48" t="n">
-        <v>-8.128197707422473e-07</v>
+        <v>-6.119109795946553e-07</v>
       </c>
     </row>
     <row r="49">
@@ -809,7 +810,7 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="B49" t="n">
-        <v>-5.878008319186361e-07</v>
+        <v>-7.098684145927605e-07</v>
       </c>
     </row>
     <row r="50">
@@ -817,7 +818,7 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="B50" t="n">
-        <v>-5.750891986302694e-07</v>
+        <v>-3.33637995757778e-07</v>
       </c>
     </row>
     <row r="51">
@@ -825,7 +826,7 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="B51" t="n">
-        <v>-2.415316715833149e-07</v>
+        <v>-3.884473123880412e-07</v>
       </c>
     </row>
     <row r="52">
@@ -833,7 +834,7 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="B52" t="n">
-        <v>-9.140891699249136e-08</v>
+        <v>3.528905869210028e-07</v>
       </c>
     </row>
     <row r="53">
@@ -841,7 +842,7 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="B53" t="n">
-        <v>5.740500834657922e-07</v>
+        <v>6.578637292077405e-07</v>
       </c>
     </row>
     <row r="54">
@@ -849,7 +850,7 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="B54" t="n">
-        <v>9.525237548330164e-07</v>
+        <v>8.534383981964998e-07</v>
       </c>
     </row>
     <row r="55">
@@ -857,7 +858,7 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="B55" t="n">
-        <v>1.462042022067014e-06</v>
+        <v>1.471327306381144e-06</v>
       </c>
     </row>
     <row r="56">
@@ -865,7 +866,7 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="B56" t="n">
-        <v>2.095813248362621e-06</v>
+        <v>2.273831241723868e-06</v>
       </c>
     </row>
     <row r="57">
@@ -873,7 +874,7 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="B57" t="n">
-        <v>3.077827138493962e-06</v>
+        <v>3.259445492549857e-06</v>
       </c>
     </row>
     <row r="58">
@@ -881,7 +882,7 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="B58" t="n">
-        <v>3.926596639532155e-06</v>
+        <v>3.901653676953056e-06</v>
       </c>
     </row>
     <row r="59">
@@ -889,7 +890,7 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="B59" t="n">
-        <v>5.298084522531493e-06</v>
+        <v>5.155106428656834e-06</v>
       </c>
     </row>
     <row r="60">
@@ -897,7 +898,7 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="B60" t="n">
-        <v>6.776907368249621e-06</v>
+        <v>6.956135772325355e-06</v>
       </c>
     </row>
     <row r="61">
@@ -905,7 +906,7 @@
         <v>0.191919191919192</v>
       </c>
       <c r="B61" t="n">
-        <v>8.868037048532388e-06</v>
+        <v>8.845047517840238e-06</v>
       </c>
     </row>
     <row r="62">
@@ -913,7 +914,7 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="B62" t="n">
-        <v>1.108289941839332e-05</v>
+        <v>1.102617544687179e-05</v>
       </c>
     </row>
     <row r="63">
@@ -921,7 +922,7 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="B63" t="n">
-        <v>1.382390786867322e-05</v>
+        <v>1.360462133873323e-05</v>
       </c>
     </row>
     <row r="64">
@@ -929,7 +930,7 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="B64" t="n">
-        <v>1.741548806674379e-05</v>
+        <v>1.728425941692221e-05</v>
       </c>
     </row>
     <row r="65">
@@ -937,7 +938,7 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="B65" t="n">
-        <v>2.15155860653159e-05</v>
+        <v>2.130397128488417e-05</v>
       </c>
     </row>
     <row r="66">
@@ -945,7 +946,7 @@
         <v>0.292929292929293</v>
       </c>
       <c r="B66" t="n">
-        <v>2.656165466693766e-05</v>
+        <v>2.677565078784028e-05</v>
       </c>
     </row>
     <row r="67">
@@ -953,7 +954,7 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="B67" t="n">
-        <v>3.242801421429797e-05</v>
+        <v>3.271994454124381e-05</v>
       </c>
     </row>
     <row r="68">
@@ -961,7 +962,7 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="B68" t="n">
-        <v>4.048128565545624e-05</v>
+        <v>4.062328912651668e-05</v>
       </c>
     </row>
     <row r="69">
@@ -969,7 +970,7 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="B69" t="n">
-        <v>5.003720706943225e-05</v>
+        <v>5.004452404555475e-05</v>
       </c>
     </row>
     <row r="70">
@@ -977,7 +978,7 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="B70" t="n">
-        <v>6.151555263173121e-05</v>
+        <v>6.165244980305835e-05</v>
       </c>
     </row>
     <row r="71">
@@ -985,7 +986,7 @@
         <v>0.393939393939394</v>
       </c>
       <c r="B71" t="n">
-        <v>7.561214582917243e-05</v>
+        <v>7.570047409612793e-05</v>
       </c>
     </row>
     <row r="72">
@@ -993,7 +994,7 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="B72" t="n">
-        <v>9.280732892941171e-05</v>
+        <v>9.275776127735656e-05</v>
       </c>
     </row>
     <row r="73">
@@ -1001,7 +1002,7 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="B73" t="n">
-        <v>0.000113865544374301</v>
+        <v>0.0001139584500883587</v>
       </c>
     </row>
     <row r="74">
@@ -1009,7 +1010,7 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0001397478539513639</v>
+        <v>0.0001397980870792653</v>
       </c>
     </row>
     <row r="75">
@@ -1017,7 +1018,7 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0001713323132963051</v>
+        <v>0.0001715386503050643</v>
       </c>
     </row>
     <row r="76">
@@ -1025,7 +1026,7 @@
         <v>0.494949494949495</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0002100130282193019</v>
+        <v>0.000209988897039166</v>
       </c>
     </row>
     <row r="77">
@@ -1033,7 +1034,7 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0002575387373350303</v>
+        <v>0.0002575229032613577</v>
       </c>
     </row>
     <row r="78">
@@ -1041,7 +1042,7 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0003155100429703204</v>
+        <v>0.0003155295574340109</v>
       </c>
     </row>
     <row r="79">
@@ -1049,7 +1050,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0003868260169819277</v>
+        <v>0.0003865640479426329</v>
       </c>
     </row>
     <row r="80">
@@ -1057,7 +1058,7 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0004733459907301466</v>
+        <v>0.0004732658069401935</v>
       </c>
     </row>
     <row r="81">
@@ -1065,7 +1066,7 @@
         <v>0.595959595959596</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0005798052779649741</v>
+        <v>0.0005799335539397049</v>
       </c>
     </row>
     <row r="82">
@@ -1073,7 +1074,7 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0007095627829878473</v>
+        <v>0.0007098362769446795</v>
       </c>
     </row>
     <row r="83">
@@ -1081,7 +1082,7 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0008688811739596266</v>
+        <v>0.0008691403719118097</v>
       </c>
     </row>
     <row r="84">
@@ -1089,7 +1090,7 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0010642319344498</v>
+        <v>0.001063678997269649</v>
       </c>
     </row>
     <row r="85">
@@ -1097,7 +1098,7 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="B85" t="n">
-        <v>0.001302443751845014</v>
+        <v>0.001302315429412032</v>
       </c>
     </row>
     <row r="86">
@@ -1105,7 +1106,7 @@
         <v>0.696969696969697</v>
       </c>
       <c r="B86" t="n">
-        <v>0.001594062927496364</v>
+        <v>0.001594090759751863</v>
       </c>
     </row>
     <row r="87">
@@ -1113,7 +1114,7 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="B87" t="n">
-        <v>0.001951366262274125</v>
+        <v>0.00195169502492457</v>
       </c>
     </row>
     <row r="88">
@@ -1121,7 +1122,7 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="B88" t="n">
-        <v>0.002388908346430514</v>
+        <v>0.002388973165728891</v>
       </c>
     </row>
     <row r="89">
@@ -1129,7 +1130,7 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="B89" t="n">
-        <v>0.002923668701554566</v>
+        <v>0.002924234701597313</v>
       </c>
     </row>
     <row r="90">
@@ -1137,7 +1138,7 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="B90" t="n">
-        <v>0.00357910666308193</v>
+        <v>0.003579231063317537</v>
       </c>
     </row>
     <row r="91">
@@ -1145,7 +1146,7 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="B91" t="n">
-        <v>0.004380547544919552</v>
+        <v>0.004380568354789942</v>
       </c>
     </row>
     <row r="92">
@@ -1153,7 +1154,7 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="B92" t="n">
-        <v>0.005361693247289966</v>
+        <v>0.005361530425018507</v>
       </c>
     </row>
     <row r="93">
@@ -1161,7 +1162,7 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="B93" t="n">
-        <v>0.006562097899529768</v>
+        <v>0.006562092715182223</v>
       </c>
     </row>
     <row r="94">
@@ -1169,7 +1170,7 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="B94" t="n">
-        <v>0.008031434054084659</v>
+        <v>0.008031601117524588</v>
       </c>
     </row>
     <row r="95">
@@ -1177,7 +1178,7 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="B95" t="n">
-        <v>0.009829831664932634</v>
+        <v>0.009830242353749718</v>
       </c>
     </row>
     <row r="96">
@@ -1185,7 +1186,7 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="B96" t="n">
-        <v>0.01203097232811743</v>
+        <v>0.01203085692871843</v>
       </c>
     </row>
     <row r="97">
@@ -1193,7 +1194,7 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="B97" t="n">
-        <v>0.01472479051928766</v>
+        <v>0.01472455052089328</v>
       </c>
     </row>
     <row r="98">
@@ -1201,7 +1202,7 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="B98" t="n">
-        <v>0.01802134002644562</v>
+        <v>0.01802178824487147</v>
       </c>
     </row>
     <row r="99">
@@ -1209,7 +1210,7 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="B99" t="n">
-        <v>0.02205624653091874</v>
+        <v>0.02205657963310629</v>
       </c>
     </row>
     <row r="100">
@@ -1217,7 +1218,7 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="B100" t="n">
-        <v>0.02699455311882026</v>
+        <v>0.0269945129926506</v>
       </c>
     </row>
     <row r="101">
@@ -1225,7 +1226,43 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0330381190422584</v>
+        <v>0.03303839830201237</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha y hora inicio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Isc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18.7</v>
       </c>
     </row>
   </sheetData>
